--- a/IHSG/RS_Industry.xlsx
+++ b/IHSG/RS_Industry.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,23 +490,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>216.84</v>
+        <v>250.97</v>
       </c>
       <c r="E2" t="n">
         <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H2" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ENRG,RATU,MEDC</t>
+          <t>MTFN,ENRG,MEDC,RATU</t>
         </is>
       </c>
     </row>
@@ -516,32 +516,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other Industrial Metals &amp; Mining</t>
+          <t>Lodging</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>155.48</v>
+        <v>212.05</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="H3" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PTRO,BRMS,INCO,NCKL,MDKA,UNTR</t>
+          <t>NATO,PSKT,MINA,ESTA,CLAY,INDO,PLAN,FITT,AKKU,HRME,PGLI,GRPH,ARTA,EAST,SHID,JIHD,SNLK</t>
         </is>
       </c>
     </row>
@@ -551,32 +551,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Gas</t>
+          <t>Metal Fabrication</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>149.74</v>
+        <v>211.51</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="H4" t="n">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RAJA,PGAS</t>
+          <t>HOPE,ISAP,NIKL,TBMS,LMSH</t>
         </is>
       </c>
     </row>
@@ -586,32 +586,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Broadcasting</t>
+          <t>Utilities - Renewable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>136.17</v>
+        <v>201.94</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F5" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="H5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SCMA,EMTK</t>
+          <t>SOFA,FUTR,OASA,BREN,PGEO,HGII,TGRA</t>
         </is>
       </c>
     </row>
@@ -621,32 +621,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Business Equipment &amp; Supplies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>132.14</v>
+        <v>195.85</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRPT,ESSA</t>
+          <t>MDRN,CASH,LION,BINO,MCAS</t>
         </is>
       </c>
     </row>
@@ -656,32 +656,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thermal Coal</t>
+          <t>Leisure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>123.19</v>
+        <v>190.3</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
+        <v>37</v>
+      </c>
+      <c r="G7" t="n">
         <v>53</v>
       </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
       <c r="H7" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BUMI,DSSA,INDY,HRUM,ADRO,PTBA,ITMG,AADI</t>
+          <t>JGLE,GOLF,PJAA,TOYS,BIKE</t>
         </is>
       </c>
     </row>
@@ -691,32 +691,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Telecom Services</t>
+          <t>Trucking</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>112.74</v>
+        <v>187.47</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="H8" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EXCL,TLKM,ISAT,MTEL</t>
+          <t>INPS,TRUK,SDMU,PURA,AKSI,MPXL,JAYA,MAHA,RCCC</t>
         </is>
       </c>
     </row>
@@ -726,32 +726,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Farm Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>105.17</v>
+        <v>183.14</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H9" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JPFA,TAPG,DSNG,LSIP,CPIN</t>
+          <t>PADI,PEGE,TRIM,LPPS,YULE,PANS,RELI</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -770,23 +770,23 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>93.48</v>
+        <v>179.8</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="G10" t="n">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>INTP,SMGR</t>
+          <t>ARCI,ANTM,PSAB,EMAS,SQMI</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other Precious Metals &amp; Mining</t>
+          <t>Lumber &amp; Wood Production</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -805,23 +805,23 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>92.73</v>
+        <v>177.64</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="H11" t="n">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MBMA,AMMN</t>
+          <t>SINI,SULI,IFII,FWCT</t>
         </is>
       </c>
     </row>
@@ -831,32 +831,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Real Estate Services</t>
+          <t>Broadcasting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>89.20999999999999</v>
+        <v>177.5</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="H12" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>KPIG,TOWR</t>
+          <t>MDIA,VIVA,EMTK,NETV,SCMA,MARI</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Banks - Regional</t>
+          <t>Education &amp; Training Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>87.20999999999999</v>
+        <v>177.27</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PNLF,BTPS,BMRI,BBTN,BBNI,BBRI,PNBN,ARTO,BBCA</t>
+          <t>BMBL,IDEA,MERI</t>
         </is>
       </c>
     </row>
@@ -901,32 +901,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Packaged Foods</t>
+          <t>Real Estate - Diversified</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81.3</v>
+        <v>176.38</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="H14" t="n">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CMRY,MYOR,INDF,ICBP</t>
+          <t>REAL,TARA,BIPP,PAMG,PWON</t>
         </is>
       </c>
     </row>
@@ -936,32 +936,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Medical Care Facilities</t>
+          <t>Oil &amp; Gas Refining &amp; Marketing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>81.26000000000001</v>
+        <v>171.96</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H15" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MIKA,HEAL</t>
+          <t>LMAX,CGAS,AKRA,KOPI</t>
         </is>
       </c>
     </row>
@@ -971,32 +971,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Real Estate - Development</t>
+          <t>Farm Products</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>80.70999999999999</v>
+        <v>170.03</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="H16" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>KIJA,BSDE,PANI,SMRA,CTRA</t>
+          <t>AMMS,NSSS,WMUU,JARR,ASHA,BTEK,AYAM,UNSP,SGRO,ANDI,SIPD,IKAN,DSFI,PTPS,PNGO,GZCO,DEWI,JAWA,TAPG,NASI,JPFA,SMAR,DSNG,STAA,CPRO,GULA,MKTR,ANJT,CSRA,AALI,NEST,SSMS,FAPA,TLDN,PSGO,AGAR,LSIP,CPIN,FISH</t>
         </is>
       </c>
     </row>
@@ -1006,32 +1006,2925 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Waste Management</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="E17" t="n">
+        <v>84</v>
+      </c>
+      <c r="F17" t="n">
+        <v>94</v>
+      </c>
+      <c r="G17" t="n">
+        <v>92</v>
+      </c>
+      <c r="H17" t="n">
+        <v>61</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>OPMS,MHKI,INOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Apparel Manufacturing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>165.8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>83</v>
+      </c>
+      <c r="F18" t="n">
+        <v>93</v>
+      </c>
+      <c r="G18" t="n">
+        <v>94</v>
+      </c>
+      <c r="H18" t="n">
+        <v>25</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>POLU,ERTX,PBRX,RICY,ACRO,TRIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Confectioners</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>162.27</v>
+      </c>
+      <c r="E19" t="n">
+        <v>82</v>
+      </c>
+      <c r="F19" t="n">
+        <v>80</v>
+      </c>
+      <c r="G19" t="n">
+        <v>88</v>
+      </c>
+      <c r="H19" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COCO,YUPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Building Products &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>162.23</v>
+      </c>
+      <c r="E20" t="n">
+        <v>81</v>
+      </c>
+      <c r="F20" t="n">
+        <v>55</v>
+      </c>
+      <c r="G20" t="n">
+        <v>58</v>
+      </c>
+      <c r="H20" t="n">
+        <v>55</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IMPC,IKAI,KUAS,KOIN,CAKK,TOTO,MLIA,KIAS,ARNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>162.02</v>
+      </c>
+      <c r="E21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" t="n">
+        <v>84</v>
+      </c>
+      <c r="G21" t="n">
+        <v>80</v>
+      </c>
+      <c r="H21" t="n">
+        <v>78</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>HDIT,CYBR,WGSH,MPIX,GOTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other Industrial Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>160.97</v>
+      </c>
+      <c r="E22" t="n">
+        <v>79</v>
+      </c>
+      <c r="F22" t="n">
+        <v>63</v>
+      </c>
+      <c r="G22" t="n">
+        <v>79</v>
+      </c>
+      <c r="H22" t="n">
+        <v>68</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NICL,TINS,ZINC,IFSH,DKFT,BRMS,ITMA,PTRO,INCO,NCKL,MDKA,SMGA,CITA,DAAZ,NICE,UNTR,MINE,HILL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Construction</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>159.39</v>
+      </c>
+      <c r="E23" t="n">
+        <v>78</v>
+      </c>
+      <c r="F23" t="n">
+        <v>79</v>
+      </c>
+      <c r="G23" t="n">
+        <v>76</v>
+      </c>
+      <c r="H23" t="n">
+        <v>72</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PTDU,PBSA,PKPK,MTPS,PPRE,KOKA,NRCA,SMKM,BBSS,SOLA,DGIK,BUKK,TOTL,RONY,ACST,MANG,IDPR,SSIA,BDKR,PTPW,WEGE,KRYA,FIMP,TOPS,PTPP,ADHI,WIKA,MEJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Integrated Freight &amp; Logistics</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>156.69</v>
+      </c>
+      <c r="E24" t="n">
+        <v>77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>86</v>
+      </c>
+      <c r="G24" t="n">
+        <v>81</v>
+      </c>
+      <c r="H24" t="n">
+        <v>59</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LOPI,PPGL,GTRA,LAJU,IPCC,KJEN,TNCA,BLOG,SAPX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Software - Application</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>155.26</v>
+      </c>
+      <c r="E25" t="n">
+        <v>76</v>
+      </c>
+      <c r="F25" t="n">
+        <v>89</v>
+      </c>
+      <c r="G25" t="n">
+        <v>83</v>
+      </c>
+      <c r="H25" t="n">
+        <v>47</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>UVCR,KIOS,RUNS,DIVA,TOSK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Conglomerates</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>155.21</v>
+      </c>
+      <c r="E26" t="n">
+        <v>75</v>
+      </c>
+      <c r="F26" t="n">
+        <v>85</v>
+      </c>
+      <c r="G26" t="n">
+        <v>68</v>
+      </c>
+      <c r="H26" t="n">
+        <v>32</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BNBR,ASII,TSPC,IMJS,JKON</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Travel Services</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>74</v>
+      </c>
+      <c r="F27" t="n">
+        <v>42</v>
+      </c>
+      <c r="G27" t="n">
+        <v>54</v>
+      </c>
+      <c r="H27" t="n">
+        <v>88</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PGJO,YELO,PDES,HAJJ,BAYU,PANR,SONA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas Drilling</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>152.63</v>
+      </c>
+      <c r="E28" t="n">
+        <v>73</v>
+      </c>
+      <c r="F28" t="n">
+        <v>98</v>
+      </c>
+      <c r="G28" t="n">
+        <v>33</v>
+      </c>
+      <c r="H28" t="n">
+        <v>13</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>APEX,BOAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Marine Shipping</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>151.72</v>
+      </c>
+      <c r="E29" t="n">
+        <v>72</v>
+      </c>
+      <c r="F29" t="n">
+        <v>76</v>
+      </c>
+      <c r="G29" t="n">
+        <v>49</v>
+      </c>
+      <c r="H29" t="n">
+        <v>54</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>GTSI,HUMI,BBRM,BULL,SOCI,ELPI,TAMU,BSML,LEAD,BESS,MITI,BLTA,TCPI,MBSS,ALII,INDX,SMDR,HATM,WINS,IPCM,HAIS,NELY,TMAS,TPMA,PSSI,PORT,PSAT,PTIS,RIGS,HITS,KLAS,KARW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Restaurants</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>150.01</v>
+      </c>
+      <c r="E30" t="n">
+        <v>71</v>
+      </c>
+      <c r="F30" t="n">
+        <v>57</v>
+      </c>
+      <c r="G30" t="n">
+        <v>43</v>
+      </c>
+      <c r="H30" t="n">
+        <v>43</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>IBOS,BAIK,RAFI,FAST,PZZA,FORE,PTSP,MAPB,ENAK,CSMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Industrial Distribution</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>149.97</v>
+      </c>
+      <c r="E31" t="n">
+        <v>70</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" t="n">
+        <v>26</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>VISI,TIRA,CSAP,HEXA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Furnishings, Fixtures &amp; Appliances</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>149.96</v>
+      </c>
+      <c r="E32" t="n">
+        <v>69</v>
+      </c>
+      <c r="F32" t="n">
+        <v>47</v>
+      </c>
+      <c r="G32" t="n">
+        <v>51</v>
+      </c>
+      <c r="H32" t="n">
+        <v>46</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LFLO,SPRE,OLIV,KICI,LMPI,LIVE,CINT,TOOL,SPTO,WOOD,GEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Residential Construction</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>148.56</v>
+      </c>
+      <c r="E33" t="n">
+        <v>68</v>
+      </c>
+      <c r="F33" t="n">
+        <v>99</v>
+      </c>
+      <c r="G33" t="n">
+        <v>99</v>
+      </c>
+      <c r="H33" t="n">
+        <v>98</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ASPI,KBAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Real Estate - Development</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>147.92</v>
+      </c>
+      <c r="E34" t="n">
+        <v>67</v>
+      </c>
+      <c r="F34" t="n">
+        <v>59</v>
+      </c>
+      <c r="G34" t="n">
+        <v>64</v>
+      </c>
+      <c r="H34" t="n">
+        <v>51</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>RISE,HBAT,KOCI,MPRO,BAPI,WINR,CSIS,CITY,SAGE,AMAN,TAMA,NASA,RELF,SWID,HOMI,LPCK,GWSA,BAPA,RBMS,APLN,POLI,BKSL,KSIX,URBN,KIJA,RODA,CBPE,NZIA,JRPT,GRIA,BSBK,GPRA,ASRI,MDLN,SATU,ADCP,DUTI,BCIP,DMAS,DILD,BSDE,SMDM,GMTD,PURI,POLL,BIKA,PPRO,SMRA,CTRA,PANI,FMII</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Railroads</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>146.57</v>
+      </c>
+      <c r="E35" t="n">
+        <v>66</v>
+      </c>
+      <c r="F35" t="n">
+        <v>73</v>
+      </c>
+      <c r="G35" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" t="n">
+        <v>66</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TAXI,SAFE,LRNA,WEHA,BIRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Textile Manufacturing</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>142.57</v>
+      </c>
+      <c r="E36" t="n">
+        <v>65</v>
+      </c>
+      <c r="F36" t="n">
+        <v>16</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>11</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ESTI,BELL,TFCO,MSJA,ARGO,INDR,MYTX,CNTX,SBAT,BRAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Real Estate Services</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>138.43</v>
+      </c>
+      <c r="E37" t="n">
+        <v>64</v>
+      </c>
+      <c r="F37" t="n">
+        <v>41</v>
+      </c>
+      <c r="G37" t="n">
+        <v>57</v>
+      </c>
+      <c r="H37" t="n">
+        <v>53</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>KOTA,DADA,ELTY,LAND,MSIE,DFAM,NIRO,KPIG,PUDP,RDTX,MTLA,BKDP,VAST,DART,NICK,CBDK,OMRE,BEST,IPAC,TOWR,PLIN,LPLI,MTSM,MKPI,SUPR,MMLP,EMDE,INPP,JSPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Utilities - Regulated Gas</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>138.04</v>
+      </c>
+      <c r="E38" t="n">
+        <v>63</v>
+      </c>
+      <c r="F38" t="n">
+        <v>92</v>
+      </c>
+      <c r="G38" t="n">
+        <v>86</v>
+      </c>
+      <c r="H38" t="n">
+        <v>89</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>RAJA,PGAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pharmaceutical Retailers</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>137.86</v>
+      </c>
+      <c r="E39" t="n">
+        <v>62</v>
+      </c>
+      <c r="F39" t="n">
+        <v>88</v>
+      </c>
+      <c r="G39" t="n">
+        <v>93</v>
+      </c>
+      <c r="H39" t="n">
+        <v>75</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>MMIX,PEVE,IKPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Household &amp; Personal Products</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>136.78</v>
+      </c>
+      <c r="E40" t="n">
+        <v>61</v>
+      </c>
+      <c r="F40" t="n">
+        <v>71</v>
+      </c>
+      <c r="G40" t="n">
+        <v>74</v>
+      </c>
+      <c r="H40" t="n">
+        <v>10</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EURO,FLMC,MRAT,MBTO,TCID,UNVR,MICE,VICI,UCID</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas Equipment &amp; Services</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>136.38</v>
+      </c>
+      <c r="E41" t="n">
+        <v>60</v>
+      </c>
+      <c r="F41" t="n">
+        <v>60</v>
+      </c>
+      <c r="G41" t="n">
+        <v>61</v>
+      </c>
+      <c r="H41" t="n">
+        <v>93</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>MKAP,ICON,SHIP,MIRA,CTBN,WOWS,RUIS,ELSA,SICO,ATLA,SUNI,ARTI,RGAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Credit Services</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="E42" t="n">
+        <v>59</v>
+      </c>
+      <c r="F42" t="n">
+        <v>20</v>
+      </c>
+      <c r="G42" t="n">
+        <v>18</v>
+      </c>
+      <c r="H42" t="n">
+        <v>37</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>IBFN,POLA,FUJI,BBLD,CFIN,VRNA,HDFA,BPFI,BFIN,ADMF,WOMF,TRUS,TIFA,DEFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Beverages - Brewers</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="E43" t="n">
+        <v>58</v>
+      </c>
+      <c r="F43" t="n">
+        <v>24</v>
+      </c>
+      <c r="G43" t="n">
+        <v>39</v>
+      </c>
+      <c r="H43" t="n">
+        <v>79</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>STRK,DLTA,MLBI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Footwear &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>133.38</v>
+      </c>
+      <c r="E44" t="n">
+        <v>57</v>
+      </c>
+      <c r="F44" t="n">
+        <v>53</v>
+      </c>
+      <c r="G44" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BATA,BIMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Insurance - Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>132.93</v>
+      </c>
+      <c r="E45" t="n">
+        <v>56</v>
+      </c>
+      <c r="F45" t="n">
+        <v>54</v>
+      </c>
+      <c r="G45" t="n">
+        <v>47</v>
+      </c>
+      <c r="H45" t="n">
+        <v>19</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ASMI,AHAP,VINS,ASJT,AMAG,ASRM,ABDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Information Technology Services</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>132.02</v>
+      </c>
+      <c r="E46" t="n">
+        <v>55</v>
+      </c>
+      <c r="F46" t="n">
+        <v>82</v>
+      </c>
+      <c r="G46" t="n">
+        <v>85</v>
+      </c>
+      <c r="H46" t="n">
+        <v>95</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>TRON,WIFI,ELIT,DCII,MLPT,ATIC,JATI,NINE,AREA,EDGE,MSTI,WIRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Infrastructure Operations</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>131.92</v>
+      </c>
+      <c r="E47" t="n">
+        <v>54</v>
+      </c>
+      <c r="F47" t="n">
+        <v>17</v>
+      </c>
+      <c r="G47" t="n">
+        <v>36</v>
+      </c>
+      <c r="H47" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>BIPI,TEBE,CMNP,JSMR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>129.28</v>
+      </c>
+      <c r="E48" t="n">
+        <v>53</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21</v>
+      </c>
+      <c r="G48" t="n">
+        <v>29</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>FILM,IPTV,BOLA,KBLV,MSKY,BHIT,BLTZ,BMTR,DYAN,VERN,RAAM,CNMA,MSIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Communication Equipment</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>128.73</v>
+      </c>
+      <c r="E49" t="n">
+        <v>52</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13</v>
+      </c>
+      <c r="G49" t="n">
+        <v>26</v>
+      </c>
+      <c r="H49" t="n">
+        <v>14</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>KETR,CCSI,MKNT,IOTF</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Aluminum</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="E50" t="n">
+        <v>51</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>19</v>
+      </c>
+      <c r="H50" t="n">
+        <v>39</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ALKA,INAI,ALMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Specialty Chemicals</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>127.54</v>
+      </c>
+      <c r="E51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" t="n">
+        <v>52</v>
+      </c>
+      <c r="G51" t="n">
+        <v>41</v>
+      </c>
+      <c r="H51" t="n">
+        <v>57</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>FPNI,INCF,POLY,CHEM,KKES,CLPI,INCI,OBMD,MDKI,SMLE,AVIA,DPNS,EKAD,OKAS,LTLS,TPIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tobacco</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>127.45</v>
+      </c>
+      <c r="E52" t="n">
+        <v>49</v>
+      </c>
+      <c r="F52" t="n">
+        <v>72</v>
+      </c>
+      <c r="G52" t="n">
+        <v>70</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>WIIM,GGRM,ITIC,HMSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Medical Care Facilities</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>126.83</v>
+      </c>
+      <c r="E53" t="n">
+        <v>48</v>
+      </c>
+      <c r="F53" t="n">
+        <v>31</v>
+      </c>
+      <c r="G53" t="n">
+        <v>28</v>
+      </c>
+      <c r="H53" t="n">
+        <v>33</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SRAJ,CARE,PRIM,LPKR,PRAY,DKHH,SAME,SILO,MTMH,BMHS,RSCH,HEAL,RSGK,MIKA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Insurance - Life</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>126.11</v>
+      </c>
+      <c r="E54" t="n">
+        <v>47</v>
+      </c>
+      <c r="F54" t="n">
+        <v>58</v>
+      </c>
+      <c r="G54" t="n">
+        <v>48</v>
+      </c>
+      <c r="H54" t="n">
+        <v>70</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>BHAT,JMAS,CASA,APIC,LIFE,PNIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Computer Hardware</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>126.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>46</v>
+      </c>
+      <c r="F55" t="n">
+        <v>62</v>
+      </c>
+      <c r="G55" t="n">
+        <v>44</v>
+      </c>
+      <c r="H55" t="n">
+        <v>56</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>LUCK,ZYRX,AXIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Telecom Services</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>124.32</v>
+      </c>
+      <c r="E56" t="n">
+        <v>45</v>
+      </c>
+      <c r="F56" t="n">
+        <v>56</v>
+      </c>
+      <c r="G56" t="n">
+        <v>31</v>
+      </c>
+      <c r="H56" t="n">
+        <v>71</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>DATA,INET,JAST,EXCL,CENT,LINK,TLKM,ISAT,LCKM,GOLD,GHON,BALI,IBST,TBIG,MTEL,TELE,DNET,CHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Specialty Business Services</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>123.24</v>
+      </c>
+      <c r="E57" t="n">
+        <v>44</v>
+      </c>
+      <c r="F57" t="n">
+        <v>67</v>
+      </c>
+      <c r="G57" t="n">
+        <v>72</v>
+      </c>
+      <c r="H57" t="n">
+        <v>84</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>JTPE,ASGR,ARKA,SOUL,MUTU,CRSN,HYGN,KING,MFMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Thermal Coal</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>121.95</v>
+      </c>
+      <c r="E58" t="n">
+        <v>43</v>
+      </c>
+      <c r="F58" t="n">
+        <v>32</v>
+      </c>
+      <c r="G58" t="n">
+        <v>32</v>
+      </c>
+      <c r="H58" t="n">
+        <v>42</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>DEWA,BUMI,INDY,AIMS,FIRE,IATA,COAL,DSSA,SGER,CNKO,GTBO,TOBA,SMMT,ADRO,HRUM,CUAN,ARII,AADI,DWGL,PTBA,BSSR,ITMG,ABMM,MBAP,KKGI,MYOH,GEMS,MCOL,DOID,BYAN,UNIQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Diagnostics &amp; Research</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>120.52</v>
+      </c>
+      <c r="E59" t="n">
+        <v>42</v>
+      </c>
+      <c r="F59" t="n">
+        <v>11</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>18</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>DGNS,PRDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Medical Distribution</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>120.49</v>
+      </c>
+      <c r="E60" t="n">
+        <v>41</v>
+      </c>
+      <c r="F60" t="n">
+        <v>25</v>
+      </c>
+      <c r="G60" t="n">
+        <v>22</v>
+      </c>
+      <c r="H60" t="n">
+        <v>17</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SOHO,SDPC,MDLA,EPMT,IRRA,ZBRA,KAEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Farm &amp; Heavy Construction Machinery</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="E61" t="n">
+        <v>40</v>
+      </c>
+      <c r="F61" t="n">
+        <v>95</v>
+      </c>
+      <c r="G61" t="n">
+        <v>75</v>
+      </c>
+      <c r="H61" t="n">
+        <v>36</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>NTBK,KOBX</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Beverages - Wineries &amp; Distilleries</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>120.06</v>
+      </c>
+      <c r="E62" t="n">
+        <v>39</v>
+      </c>
+      <c r="F62" t="n">
+        <v>36</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>BEER,WINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tools &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>119.26</v>
+      </c>
+      <c r="E63" t="n">
+        <v>38</v>
+      </c>
+      <c r="F63" t="n">
+        <v>30</v>
+      </c>
+      <c r="G63" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" t="n">
+        <v>76</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>BAUT,APII,BOLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Other Precious Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>118.08</v>
+      </c>
+      <c r="E64" t="n">
+        <v>37</v>
+      </c>
+      <c r="F64" t="n">
+        <v>8</v>
+      </c>
+      <c r="G64" t="n">
+        <v>16</v>
+      </c>
+      <c r="H64" t="n">
+        <v>77</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>MBMA,AMMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Specialty Industrial Machinery</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>117.13</v>
+      </c>
+      <c r="E65" t="n">
+        <v>36</v>
+      </c>
+      <c r="F65" t="n">
+        <v>75</v>
+      </c>
+      <c r="G65" t="n">
+        <v>71</v>
+      </c>
+      <c r="H65" t="n">
+        <v>63</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AMIN,SEMA,PTMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>Specialty Retail</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D66" t="n">
+        <v>115.66</v>
+      </c>
+      <c r="E66" t="n">
+        <v>35</v>
+      </c>
+      <c r="F66" t="n">
+        <v>38</v>
+      </c>
+      <c r="G66" t="n">
+        <v>25</v>
+      </c>
+      <c r="H66" t="n">
+        <v>35</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>HADE,GLOB,DAYA,DOSS,ERAL,ECII,KONI,MAPA,ERAA,ACES</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Auto Parts</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="E67" t="n">
+        <v>34</v>
+      </c>
+      <c r="F67" t="n">
+        <v>15</v>
+      </c>
+      <c r="G67" t="n">
+        <v>14</v>
+      </c>
+      <c r="H67" t="n">
+        <v>41</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>INDS,AEGS,KAQI,AUTO,DRMA,LPIN,PART,GJTL,SMSM,GDYR,TYRE,KMTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Publishing</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>114.42</v>
+      </c>
+      <c r="E68" t="n">
+        <v>33</v>
+      </c>
+      <c r="F68" t="n">
+        <v>78</v>
+      </c>
+      <c r="G68" t="n">
+        <v>63</v>
+      </c>
+      <c r="H68" t="n">
+        <v>97</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ABBA,TMPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Beverages - Non-Alcoholic</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>113.17</v>
+      </c>
+      <c r="E69" t="n">
+        <v>32</v>
+      </c>
+      <c r="F69" t="n">
+        <v>23</v>
+      </c>
+      <c r="G69" t="n">
+        <v>15</v>
+      </c>
+      <c r="H69" t="n">
+        <v>22</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>GRPM,ADES,KINO,ALTO,ULTJ,CLEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="E70" t="n">
+        <v>31</v>
+      </c>
+      <c r="F70" t="n">
+        <v>64</v>
+      </c>
+      <c r="G70" t="n">
+        <v>65</v>
+      </c>
+      <c r="H70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ADMG,BRPT,MOLI,UNIC,HALO,AGII,SRSN,SBMA,BMSR,ESSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Advertising Agencies</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="E71" t="n">
+        <v>30</v>
+      </c>
+      <c r="F71" t="n">
+        <v>35</v>
+      </c>
+      <c r="G71" t="n">
+        <v>27</v>
+      </c>
+      <c r="H71" t="n">
+        <v>73</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>DOOH,FORU,MNCN,DMMX</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Insurance - Diversified</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>110.49</v>
+      </c>
+      <c r="E72" t="n">
+        <v>29</v>
+      </c>
+      <c r="F72" t="n">
+        <v>50</v>
+      </c>
+      <c r="G72" t="n">
+        <v>56</v>
+      </c>
+      <c r="H72" t="n">
+        <v>52</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>GSMF,MTWI,LPGI,ASDM,TUGU,YOII,ASBI,SMMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Medical Instruments &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>110.08</v>
+      </c>
+      <c r="E73" t="n">
+        <v>28</v>
+      </c>
+      <c r="F73" t="n">
+        <v>61</v>
+      </c>
+      <c r="G73" t="n">
+        <v>40</v>
+      </c>
+      <c r="H73" t="n">
+        <v>34</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>MEDS,SURI,OMED,MARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Staffing &amp; Employment Services</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>110.03</v>
+      </c>
+      <c r="E74" t="n">
+        <v>27</v>
+      </c>
+      <c r="F74" t="n">
+        <v>65</v>
+      </c>
+      <c r="G74" t="n">
+        <v>69</v>
+      </c>
+      <c r="H74" t="n">
+        <v>9</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>TFAS,SOSS,VTNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Paper &amp; Paper Products</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>109.91</v>
+      </c>
+      <c r="E75" t="n">
+        <v>26</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>52</v>
+      </c>
+      <c r="H75" t="n">
+        <v>31</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>INTD,INKP,TKIM,ALDO,SPMA,INRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Electronics &amp; Computer Distribution</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="E76" t="n">
+        <v>25</v>
+      </c>
+      <c r="F76" t="n">
+        <v>49</v>
+      </c>
+      <c r="G76" t="n">
+        <v>45</v>
+      </c>
+      <c r="H76" t="n">
+        <v>21</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>SLIS,GLVA,PMUI,MTDL</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Packaged Foods</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>108.33</v>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="n">
+        <v>26</v>
+      </c>
+      <c r="G77" t="n">
+        <v>34</v>
+      </c>
+      <c r="H77" t="n">
+        <v>23</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>DPUM,ENZO,FOOD,OILS,BWPT,BRRC,PSDN,BEEF,ISEA,SKBM,TAYS,SKLT,SIMP,DMND,PCAR,CMRY,AISA,WAPO,MAIN,BUDI,MYOR,CEKA,GUNA,CAMP,TRGU,BOBA,MAXI,MGRO,CRAB,IPPE,GOOD,TBLA,ROTI,HOKI,PMMP,CBUT,INDF,STTP,OBAT,ICBP,NAYZ,KEJU</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="E17" t="n">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Rental &amp; Leasing Services</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>23</v>
+      </c>
+      <c r="F78" t="n">
+        <v>66</v>
+      </c>
+      <c r="G78" t="n">
+        <v>87</v>
+      </c>
+      <c r="H78" t="n">
+        <v>85</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>WIDI,ASSA,SKRN,TRJA,BPTR,SMIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Auto &amp; Truck Dealerships</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="E79" t="n">
+        <v>22</v>
+      </c>
+      <c r="F79" t="n">
+        <v>43</v>
+      </c>
+      <c r="G79" t="n">
+        <v>12</v>
+      </c>
+      <c r="H79" t="n">
+        <v>15</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>BOGA,CARS,IMAS,ASLC,MPMX,PMJS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Packaging &amp; Containers</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>106.59</v>
+      </c>
+      <c r="E80" t="n">
+        <v>21</v>
+      </c>
+      <c r="F80" t="n">
+        <v>33</v>
+      </c>
+      <c r="G80" t="n">
+        <v>42</v>
+      </c>
+      <c r="H80" t="n">
+        <v>45</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>EPAC,ESIP,PTMR,TALF,YPAS,PPRI,PICO,ASPR,SMKL,BRNA,PBID,KDSI,FASW,IGAR,IPOL,AKPI,TRST,SWAT,APLI,PDPP,PACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>106.39</v>
+      </c>
+      <c r="E81" t="n">
+        <v>20</v>
+      </c>
+      <c r="F81" t="n">
+        <v>51</v>
+      </c>
+      <c r="G81" t="n">
+        <v>55</v>
+      </c>
+      <c r="H81" t="n">
+        <v>80</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>KRAS,GGRP,BAJA,ISSP,GDST,BTON,LABA</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Food Distribution</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>106.37</v>
+      </c>
+      <c r="E82" t="n">
+        <v>19</v>
+      </c>
+      <c r="F82" t="n">
+        <v>29</v>
+      </c>
+      <c r="G82" t="n">
+        <v>38</v>
+      </c>
+      <c r="H82" t="n">
+        <v>58</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>AYLS,TGUK,KMDS,WICO,TGKA,BUAH</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Utilities - Independent Power Producers</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>104.16</v>
+      </c>
+      <c r="E83" t="n">
+        <v>18</v>
+      </c>
+      <c r="F83" t="n">
+        <v>46</v>
+      </c>
+      <c r="G83" t="n">
+        <v>60</v>
+      </c>
+      <c r="H83" t="n">
+        <v>91</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>KEEN,MPOW,POWR</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>103.71</v>
+      </c>
+      <c r="E84" t="n">
+        <v>17</v>
+      </c>
+      <c r="F84" t="n">
+        <v>18</v>
+      </c>
+      <c r="G84" t="n">
+        <v>11</v>
+      </c>
+      <c r="H84" t="n">
+        <v>8</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>CTTH,BATR,WSBP,SMBR,INTP,WTON,SMCB,AMFG,SMGR,CMNT,BEBS,BLES,NAIK</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Asset Management</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>16</v>
+      </c>
+      <c r="F85" t="n">
+        <v>7</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" t="n">
+        <v>44</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>KREN,SRTG,VICO,PALM,BPII,SFAN,AMOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Medical Devices</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>102.07</v>
+      </c>
+      <c r="E86" t="n">
+        <v>15</v>
+      </c>
+      <c r="F86" t="n">
+        <v>40</v>
+      </c>
+      <c r="G86" t="n">
+        <v>62</v>
+      </c>
+      <c r="H86" t="n">
+        <v>49</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>NANO,LABS,CHEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>100</v>
+      </c>
+      <c r="E87" t="n">
+        <v>14</v>
+      </c>
+      <c r="F87" t="n">
+        <v>48</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>RLCO,PJHB</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Internet Content &amp; Information</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E88" t="n">
+        <v>13</v>
+      </c>
+      <c r="F88" t="n">
+        <v>27</v>
+      </c>
+      <c r="G88" t="n">
+        <v>21</v>
+      </c>
+      <c r="H88" t="n">
+        <v>60</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>DIGI,NFCX,AWAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Airlines</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="E89" t="n">
+        <v>12</v>
+      </c>
+      <c r="F89" t="n">
+        <v>69</v>
+      </c>
+      <c r="G89" t="n">
+        <v>96</v>
+      </c>
+      <c r="H89" t="n">
+        <v>74</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>GIAA,CMPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Electrical Equipment &amp; Parts</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="E90" t="n">
+        <v>11</v>
+      </c>
+      <c r="F90" t="n">
+        <v>28</v>
+      </c>
+      <c r="G90" t="n">
+        <v>59</v>
+      </c>
+      <c r="H90" t="n">
+        <v>81</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>IKBI,JECC,SCCO,VOKS,KBLM,MENN,KBLI</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Agricultural Inputs</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="E91" t="n">
+        <v>10</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>40</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NPGF,SAMF,DGWG,BISI</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Banks - Regional</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>95.23</v>
+      </c>
+      <c r="E92" t="n">
+        <v>9</v>
+      </c>
+      <c r="F92" t="n">
+        <v>10</v>
+      </c>
+      <c r="G92" t="n">
+        <v>4</v>
+      </c>
+      <c r="H92" t="n">
+        <v>24</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>BNLI,BBYB,BNBA,DNAR,BGTG,BBHI,BVIC,BSIM,BACA,BBKP,BEKS,AGRS,BABP,PNBS,INPC,BJTM,BNII,BBTN,BTPS,AMAR,MAYA,NISP,MCOR,BNGA,BCIC,AGRO,BINA,BBNI,BDMN,BTPN,BKSW,BMRI,BMAS,BBRI,BJBR,PNLF,MASB,NOBU,BBMD,MEGA,ARTO,BBSI,SDRA,PNBN,BBCA,BRIS,BANK,BSWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Internet Retail</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>94.59</v>
+      </c>
+      <c r="E93" t="n">
+        <v>8</v>
+      </c>
+      <c r="F93" t="n">
+        <v>39</v>
+      </c>
+      <c r="G93" t="n">
+        <v>6</v>
+      </c>
+      <c r="H93" t="n">
+        <v>12</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>BELI,BUKA</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="E94" t="n">
+        <v>7</v>
+      </c>
+      <c r="F94" t="n">
+        <v>19</v>
+      </c>
+      <c r="G94" t="n">
+        <v>10</v>
+      </c>
+      <c r="H94" t="n">
+        <v>29</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>PYFA,MERK,DVLA,SIDO,INAF,PEHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Home Improvement Retail</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="E95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" t="n">
+        <v>12</v>
+      </c>
+      <c r="G95" t="n">
+        <v>91</v>
+      </c>
+      <c r="H95" t="n">
+        <v>48</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>DEPO,KLIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="E96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" t="n">
         <v>1</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>16</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>LAPD,META,ENVY,KAYU,PURE,SKYB,SMRU,TRAM,CPRI,TRIO,POSA,MTRA,BTEL,SRIL,TRIL,HKMU,DUCK,MABA,WSKT,ARMY,NUSA,TDPM,UNIT,DEAL,SIMA,SUGI,ETWA,OCAP,SCPI,RIMO,GAMA,POOL,CBMF,TECH,PLAS,COWL,WMPP,MAGP,LMAS,GOLL,LCGP,IIKP,KBRI,HOTL,HOME,BOSS,JSKY</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Department Stores</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>88.26000000000001</v>
+      </c>
+      <c r="E97" t="n">
+        <v>4</v>
+      </c>
+      <c r="F97" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" t="n">
+        <v>17</v>
+      </c>
+      <c r="H97" t="n">
+        <v>28</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>MLPL,RALS,LPPF,MAPI,MPPA,UFOE,HERO,MDIY</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Grocery Stores</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" t="n">
         <v>14</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G98" t="n">
+        <v>35</v>
+      </c>
+      <c r="H98" t="n">
+        <v>6</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>RANC,MIDI,AMRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Airports &amp; Air Services</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6</v>
+      </c>
+      <c r="G99" t="n">
+        <v>9</v>
+      </c>
+      <c r="H99" t="n">
+        <v>94</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CASS,HELI</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Apparel Retail</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="E100" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MAPA,ERAA,ACES</t>
+      <c r="F100" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>13</v>
+      </c>
+      <c r="H100" t="n">
+        <v>5</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>BABY,ZONE</t>
         </is>
       </c>
     </row>
